--- a/신고신저가_20260831.xlsx
+++ b/신고신저가_20260831.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="00C00000"/>
     </font>
@@ -76,15 +77,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,84 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 미국은 실적이 확인된 소프트웨어와 금리·규제 부담이 커진 유틸리티 및 하드웨어가 선명하게 갈렸다. 아시아에서는 에너지와 전력의 일부 종목만 강했고 주요 지수는 약세여서, 지수보다 실적과 규제에 따른 종목 선별이 강한 장이었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/28): 소프트웨어의 실적 강세가 시장 전체의 금리 부담을 이기지는 못했다. 엘라스틱은 AI 수요와 가이던스 상향으로 19.3% 올랐고 기술서비스는 신고가 22종을 기록했다. 반면 산불 책임 보호 협상이 무산된 PG&amp;E는 7.5% 내렸으며 유틸리티에서는 신저가가 9종 나왔다. 연준 의장의 물가 경계 발언 뒤 금리 인상 가능성이 높아지면서 반도체 장비와 전력 인프라도 함께 약해졌다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/31): 전력과 내수 방어주가 반도체 장비의 약세를 일부 상쇄했다. 간사이전력이 장중 6.6% 오르며 전력 업종을 이끌었지만, 레이저텍은 시장 기대에 못 미친 연간 가이던스 부담이 이어져 5.4% 내렸다. 닛케이는 장중 1.3% 하락해 신고가 종목의 확산은 제한적이었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/31): 지수는 약했지만 KE홀딩스가 장중 4.1% 올라 단독 신고가 흐름을 만들었다. 항셍테크는 장중 1.2% 하락했고 신규 촉매가 확인되지 않아 부동산 플랫폼의 개별 수급 성격이 강한 움직임으로 판단한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/31): 석유와 의료기기가 지수 약세 속 상대적으로 강했다. 페트로차이나와 시노펙이 신고가를 기록했고, 시노펙은 상반기 순이익 증가와 정제마진 개선이 근거가 됐다. 화샤은행은 중간배당 미실시 발표 뒤 6.4% 내렸고, 유니트리는 상장 직후 고평가 해소 과정이 이어졌다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①엘라스틱의 상승이 다른 소프트웨어 실적주로 확산되는지 확인한다. ②캘리포니아 산불 책임 제도 변화가 PG&amp;E의 2030년 투자계획을 실제로 축소시키는지 본다. ③일본·홍콩·중국의 장 마감 후 전력·에너지 강세와 지수 약세가 유지되는지 재확인한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ 배울점: 같은 날에도 주가는 서로 다른 손잡이로 움직인다. 엘라스틱은 AI 사용 증가가 매출 수량과 가이던스를 높였고, 그 결과 미래 이익 기대가 올라 주가가 뛰었다. 반대로 PG&amp;E는 산불 책임 보호가 약해지면서 예상 비용과 투자계획의 불확실성이 커졌고, 이익 전망과 멀티플이 동시에 눌렸다. 다음 확인점은 엘라스틱의 남은계약가치와 PG&amp;E의 자본투자 계획 변경 여부다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 미국은 2026-08-28 금요일 마감분이다. 일본·홍콩·중국은 2026-08-31 오전 장중 스냅샷이므로 마감 수치가 아니며, 미국 지수 CSV는 2026-08-27 값이어서 2026-08-28 지수 방향은 원시 시세와 마감 보도로 교차확인했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +791,19 @@
       <c r="C2" t="n">
         <v>7730.99</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>5.67</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>2.21</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="4" t="n">
         <v>12.94</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +829,19 @@
       <c r="C3" t="n">
         <v>26541.35</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>1.57</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>1.82</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="4" t="n">
         <v>8.58</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="5" t="n">
         <v>-1.4</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="4" t="n">
         <v>14.2</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +867,19 @@
       <c r="C4" t="n">
         <v>6621.2</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>-4.21</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>-4.22</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>16.92</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="5" t="n">
         <v>-19.11</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="4" t="n">
         <v>57.12</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +905,19 @@
       <c r="C5" t="n">
         <v>65307.96</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>-1.25</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>-1.07</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="4" t="n">
         <v>6.31</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="5" t="n">
         <v>-1.54</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="4" t="n">
         <v>29.74</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +943,19 @@
       <c r="C6" t="n">
         <v>3941.68</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>-0.27</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="4" t="n">
         <v>1.54</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="4" t="n">
         <v>2.86</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="5" t="n">
         <v>-3.27</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="5" t="n">
         <v>-0.68</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +981,19 @@
       <c r="C7" t="n">
         <v>4578.63</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="5" t="n">
         <v>-0.66</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="4" t="n">
         <v>0.34</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="5" t="n">
         <v>-0.21</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="5" t="n">
         <v>-6.84</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>-1.11</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +1019,19 @@
       <c r="C8" t="n">
         <v>25351.27</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="5" t="n">
         <v>-0.91</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>-0.65</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="5" t="n">
         <v>-2.06</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="5" t="n">
         <v>-0.18</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="5" t="n">
         <v>-1.09</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1057,19 @@
       <c r="C9" t="n">
         <v>4550.49</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="5" t="n">
         <v>-1.19</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>-0.95</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="5" t="n">
         <v>-5.77</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="5" t="n">
         <v>-8.35</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="5" t="n">
         <v>-17.5</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1188,7 @@
       <c r="F2" t="n">
         <v>21</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1229,7 @@
       <c r="F3" t="n">
         <v>5</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1270,7 @@
       <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1311,7 @@
       <c r="F5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1352,7 @@
       <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1393,7 @@
       <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1434,7 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1475,7 @@
       <c r="F9" t="n">
         <v>-1</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1434,7 +1516,7 @@
       <c r="F10" t="n">
         <v>-2</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1475,7 +1557,7 @@
       <c r="F11" t="n">
         <v>-2</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1516,7 +1598,7 @@
       <c r="F12" t="n">
         <v>-2</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1557,7 +1639,7 @@
       <c r="F13" t="n">
         <v>-2</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1598,7 +1680,7 @@
       <c r="F14" t="n">
         <v>-5</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1639,7 +1721,7 @@
       <c r="F15" t="n">
         <v>-5</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1680,7 +1762,7 @@
       <c r="F16" t="n">
         <v>-9</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +2006,7 @@
       <c r="F22" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1965,7 +2047,7 @@
       <c r="F23" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2006,7 +2088,7 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2045,7 +2127,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2086,7 +2168,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2125,7 +2207,7 @@
       <c r="F27" t="n">
         <v>-2</v>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2677,7 +2759,7 @@
       <c r="F41" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2718,7 +2800,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3393,7 +3475,7 @@
       <c r="F59" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3432,7 +3514,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3473,7 +3555,7 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3512,7 +3594,7 @@
       <c r="F62" t="n">
         <v>-1</v>
       </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3553,7 +3635,7 @@
       <c r="F63" t="n">
         <v>-1</v>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -4101,30 +4183,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4145,90 +4228,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4250,58 +4338,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>하루 3.2% 상승했고 기술서비스 신고가가 22종으로 확산됐지만 반도체 장비는 약했다.</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>31.3</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4321,58 +4414,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>하루 1.1% 하락했으며 헬스케어 신고·신저가가 각각 2종으로 방향성이 갈렸다.</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>14.2</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>6</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4392,58 +4490,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>하루 0.7% 내렸지만 금융 신고가가 신저가보다 5종 많아 내부 흐름은 견조했다.</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4463,58 +4566,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>하루 1.1% 하락했고 3개월 수익률도 마이너스여서 소비 경기 기대가 약하다.</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>-4.9</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4534,58 +4642,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>하루 1.1% 내렸지만 AT&amp;T가 신고가를 기록해 통신 방어주는 상대적으로 강했다.</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4605,58 +4718,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>하루 0.9% 하락했고 생산·산업서비스의 신저가가 늘어 설비주 차익실현이 두드러졌다.</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>15.9</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4676,58 +4794,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>하루 1.4% 하락하고 한 달 수익률도 마이너스여서 방어주 선호가 약했다.</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4747,58 +4870,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>하루 0.2% 내렸지만 연간 수익률 41.2%로 선두를 유지해 추세는 강하다.</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>6.2</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>41.2</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4818,58 +4946,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>하루 0.8% 하락했고 신저가 9종이 나와 금리와 산불 규제 부담이 함께 반영됐다.</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-3.9</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4889,58 +5022,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>하루 0.8% 하락했지만 주간 1.5% 상승과 비철금속 신고가가 하방을 제한했다.</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4960,58 +5098,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>하루 1.0% 하락했고 금리 인상 가능성 재평가가 리츠 멀티플을 눌렀다.</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5031,58 +5174,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>21.5</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>6</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5102,58 +5246,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5173,58 +5318,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-5.8</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>14</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5244,58 +5390,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>7</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5315,58 +5462,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>13</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5386,58 +5534,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5457,58 +5606,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-7.3</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>49.5</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5528,58 +5678,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>15.3</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>10</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5599,58 +5750,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>-3.1</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>31.5</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5670,58 +5822,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>8.9</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>16.5</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>9</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5741,58 +5894,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>11</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5812,58 +5966,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>12.9</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>7.7</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>12</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5883,58 +6038,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5954,58 +6110,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>5.7</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>15</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6025,58 +6182,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>6.7</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>50.2</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6096,58 +6254,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>29.4</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6167,58 +6326,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6238,58 +6398,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6309,58 +6470,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-4.7</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-14.1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6380,56 +6542,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6447,58 +6610,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>장중 0.9% 하락했으며 연간 수익률 40.7%에 따른 차익실현 성격이 강했다.</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>40.7</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6518,58 +6686,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>장중 0.7% 내렸지만 주간 2.8% 상승해 단기 상승분 일부를 반납했다.</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6589,58 +6762,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>장중 0.4% 상승했고 한 달 13.0% 올라 중국 기술군 중 상대 강도가 높았다.</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6660,56 +6838,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>장중 1.3% 하락했고 3개월 17.1% 내려 신에너지차 약세가 이어졌다.</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-13.9</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6727,58 +6910,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>장중 0.3% 상승했지만 3개월 수익률은 마이너스라 추세 반전은 확인되지 않았다.</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-11.1</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-18</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>12</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6798,56 +6986,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>장중 1.5% 하락했고 3개월 21.0% 내려 태양광 공급과잉 부담이 지속됐다.</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-21</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6865,58 +7058,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>장중 0.5% 하락하고 한 달 7.1% 내려 주류 소비 회복 기대가 약했다.</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="6" t="n">
+      <c r="F39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="9" t="n">
         <v>-7.1</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-6</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-21.5</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>13</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>302.8</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6936,58 +7134,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>장중 0.4% 올랐지만 화샤은행 급락으로 은행 내부 종목 차별화가 컸다.</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>6</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7007,58 +7210,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>장중 3.0% 급락해 한 달 상승분 일부를 반납했고 금속주 변동성이 확대됐다.</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>7.3</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-4.6</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>5</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>41.8</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7078,58 +7286,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>장중 0.7% 상승하고 주간 5.2% 올라 정책 기대에 따른 단기 반등이 이어졌다.</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-6.2</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-16.6</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>11</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-6.6</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7149,58 +7362,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>장중 0.5% 내렸지만 주간 3.0% 올라 증권주 단기 수급은 아직 살아 있다.</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7220,58 +7438,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>장중 1.3% 하락했지만 마인드레이 신고가로 의료기기 내부 강세는 남았다.</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="H44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
+      <c r="I44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>58.4</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7291,58 +7514,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>장중 0.4% 하락하고 한 달 4.2% 내려 소비 회복의 확산은 아직 약하다.</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-15.8</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>72.7</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7354,7 +7582,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-3"/>
@@ -7366,7 +7594,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-2.3"/>
@@ -7378,7 +7606,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-7.1"/>
@@ -7390,7 +7618,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-21"/>
@@ -7402,7 +7630,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-21.5"/>
@@ -7414,7 +7642,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7426,7 +7654,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7438,7 +7666,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7450,7 +7678,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7462,7 +7690,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7474,7 +7702,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7588,12 +7816,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7637,10 +7865,10 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7689,10 +7917,10 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7741,19 +7969,19 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 세일즈포스(기업용 CRM SaaS): 2분기 매출 11% 증가에 연간 EPS 가이던스 중간값 18% 상향</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7797,10 +8025,14 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>AT&amp;T(통신): 3분기 실적 발표 일정 공지 외 신규 촉매 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7849,10 +8081,10 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7901,14 +8133,14 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 서비스나우(기업 업무자동화 플랫폼): 세일즈포스 호실적에 대형 소프트웨어 동반 강세</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7961,14 +8193,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) TJX(티제이맥스·마셜스 할인 유통): 마막스 부문 둔화를 짚은 투자의견 하향 여파</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8017,14 +8249,14 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) 어도비(크리에이티브·문서 소프트웨어): 선행 PER 11배 저평가 부각되며 섹터 랠리에 동반</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8073,15 +8305,15 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8129,10 +8361,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8181,15 +8413,15 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8233,10 +8465,10 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8285,15 +8517,15 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8337,10 +8569,10 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8389,15 +8621,15 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8445,15 +8677,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8495,15 +8727,15 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8547,10 +8779,10 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8599,10 +8831,10 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8653,19 +8885,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr">
+      <c r="N21" s="10" t="inlineStr">
         <is>
           <t>(전일) 아틀라시안(지라·컨플루언스 협업 도구): 세일즈포스발 SaaS 재평가에 동반 상승</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8709,10 +8941,10 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8761,10 +8993,10 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8811,14 +9043,14 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr">
+      <c r="N24" s="10" t="inlineStr">
         <is>
           <t>(전일) 페로비알(유료도로·공항 인프라 운영): 특별한 뉴스 없음(개별 약세 지속)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8867,15 +9099,15 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="8" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8919,15 +9151,19 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>PG&amp;E(캘리포니아 전력): 산불 책임 관련 보험사 구상권 제한 협상 무산</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8971,15 +9207,15 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" s="8" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9023,10 +9259,10 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="8" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9075,15 +9311,15 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="8" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9125,10 +9361,10 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" s="8" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9177,10 +9413,10 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" s="8" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9233,15 +9469,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N32" s="8" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9285,15 +9521,15 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" s="8" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9337,15 +9573,15 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" s="8" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9389,15 +9625,15 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="8" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9445,15 +9681,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N36" s="8" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9497,15 +9733,15 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" s="8" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9553,15 +9789,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N38" s="8" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9605,15 +9841,15 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" s="8" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9657,10 +9893,10 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" s="8" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9709,15 +9945,15 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" s="8" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9759,15 +9995,19 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" s="8" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr">
+        <is>
+          <t>제너럴밀스(가공식품): 특별한 회사 뉴스 없음(방어주 수급 영향 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9811,10 +10051,10 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="8" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9863,10 +10103,10 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" s="8" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9915,10 +10155,10 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" s="8" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9967,15 +10207,15 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" s="8" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10019,15 +10259,15 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" s="8" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10071,10 +10311,10 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="8" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10123,10 +10363,10 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" s="8" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10179,10 +10419,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N50" s="8" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10235,15 +10475,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N51" s="8" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10287,10 +10527,10 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" s="8" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10339,14 +10579,14 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" s="8" t="inlineStr">
+      <c r="N53" s="10" t="inlineStr">
         <is>
           <t>(전일) 벌링턴스토어스(할인 의류 유통): 2분기 매출 컨센 미달, 동일점포매출 둔화 부각</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10395,10 +10635,10 @@
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" s="8" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10447,10 +10687,10 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="8" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10497,15 +10737,15 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="8" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10551,15 +10791,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N57" s="8" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr">
+        <is>
+          <t>INNIO(가스엔진·발전설비): 특별한 회사 뉴스 없음(신규 상장 변동성 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10601,10 +10845,14 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" s="8" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr">
+        <is>
+          <t>GFL(폐기물 처리): 특별한 회사 뉴스 없음(인수 기대와 수급 영향 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10657,15 +10905,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N59" s="8" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10709,10 +10957,10 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" s="8" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10761,10 +11009,10 @@
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" s="8" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10813,15 +11061,15 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" s="8" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10861,10 +11109,10 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" s="8" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10915,10 +11163,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N64" s="8" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10971,15 +11219,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N65" s="8" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11023,15 +11271,19 @@
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" s="8" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr">
+        <is>
+          <t>스털링인프라(전문 건설): 특별한 회사 뉴스 없음(AI 전력 인프라 차익실현 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11073,10 +11325,10 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" s="8" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11127,15 +11379,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N68" s="8" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11179,10 +11431,10 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" s="8" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11231,15 +11483,15 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" s="8" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11287,15 +11539,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N71" s="8" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11339,10 +11591,10 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" s="8" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11393,10 +11645,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N73" s="8" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11447,19 +11699,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N74" s="8" t="inlineStr">
+      <c r="N74" s="10" t="inlineStr">
         <is>
           <t>(전일) 제이프로그(소프트웨어 배포·저장소 관리): 섹터 전반 랠리 편승, 개별 재료 미확인</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11503,10 +11755,10 @@
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" s="8" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11555,19 +11807,19 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" s="8" t="inlineStr">
+      <c r="N76" s="10" t="inlineStr">
         <is>
           <t>(전일) 호멜푸드(스팸 등 육가공 식품): 3분기 매출 컨센 미달에 연간 매출 가이던스 하향</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11607,15 +11859,15 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" s="8" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11659,15 +11911,19 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" s="8" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr">
+        <is>
+          <t>프리덤홀딩(온라인 증권·핀테크): 특별한 신규 촉매 없음(최근 실적 강세 연장 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11711,15 +11967,15 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" s="8" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B80" s="7" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11763,15 +12019,19 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="8" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr">
+        <is>
+          <t>노바(반도체 계측): 금리 재평가 속 반도체 장비주 전반 약세</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11815,10 +12075,10 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" s="8" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11867,15 +12127,15 @@
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" s="8" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11919,15 +12179,15 @@
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" s="8" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11971,10 +12231,14 @@
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" s="8" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr">
+        <is>
+          <t>제너랙(비상발전기): 회사 신규 뉴스 없이 전력·그리드 종목 동반 약세</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12027,15 +12291,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N85" s="8" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12079,15 +12343,15 @@
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" s="8" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12131,15 +12395,15 @@
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" s="8" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12181,15 +12445,15 @@
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" s="8" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12237,15 +12501,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N89" s="8" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr">
+        <is>
+          <t>엘라스틱(검색·관측 소프트웨어): AI 수요로 1분기 실적 상회·FY27 매출 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B90" s="7" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12293,15 +12561,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N90" s="8" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B91" s="7" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12345,7 +12613,7 @@
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
-      <c r="N91" s="8" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N91"/>
@@ -12451,7 +12719,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12504,19 +12772,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 리크루트홀딩스(구인구직 플랫폼·인재파견): 증권사 두 곳이 목표주가를 2만엔 안팎으로 상향</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12558,15 +12826,19 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>소니(게임·콘텐츠·전자): 특별한 회사 뉴스 없음(개별 수급 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12612,15 +12884,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>NTT(통신): 특별한 회사 뉴스 없음(방어적 통신주 수급 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12664,15 +12940,19 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>스즈키(자동차): 특별한 회사 뉴스 없음(자동차 업종 순환매 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12718,15 +12998,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12770,15 +13050,19 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>레이저텍(반도체 검사장비): 시장 기대를 밑돈 FY27 가이던스 부담 지속</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12820,15 +13104,19 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>간사이전력(전력): 특별한 회사 뉴스 없음(전력주 수급 영향 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12870,15 +13158,19 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>오빅(기업용 소프트웨어): 특별한 회사 뉴스 없음(소프트웨어 강세 연장 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12922,10 +13214,14 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>에바라(펌프·반도체 장비): 특별한 회사 뉴스 없음(기계 업종 약세 영향 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12978,14 +13274,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 시즈오카파이낸셜그룹(시즈오카현 기반 지방은행 지주): 금리 상승 기대에 지방은행 순환매 지속</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13032,7 +13328,7 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>(전일) 니테라(점화플러그 등 자동차부품): 특별한 뉴스 없음, 미국 부품사업 철수 여진 추정</t>
         </is>
@@ -13142,7 +13438,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13189,19 +13485,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 한소제약(중국 항암·중추신경 혁신신약 개발사): 상반기 호실적에 외국계 목표주가 상향</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13245,7 +13541,11 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>KE홀딩스(주택 중개 플랫폼): 특별한 회사 뉴스 없음(부동산주 개별 수급 추정)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N3"/>
@@ -13351,12 +13651,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13396,15 +13696,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>페트로차이나(석유·가스): 중간실적 공시와 쿤룬캐피털 증자 참여 발표</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13444,15 +13748,19 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>시노펙(정유·석화): 상반기 순이익 19% 증가·정제마진 개선 재평가</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13496,15 +13804,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>유니트리(휴머노이드 로봇): 상장 급등 뒤 실적 대비 고평가 부담으로 조정 지속</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13546,15 +13858,19 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>무위안푸드(양돈): 특별한 회사 뉴스 없음(공급·돈가 기대 영향 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13596,15 +13912,19 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>마인드레이(의료기기): 특별한 회사 뉴스 없음(의료기기 수급 영향 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13652,7 +13972,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>화샤은행(은행): 2026년 중간배당 미실시 발표 뒤 급락</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N7"/>
